--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136426692</v>
+        <v>136621869</v>
       </c>
       <c r="B6" t="n">
-        <v>80589</v>
+        <v>91540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,34 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>3286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Getbergstjärn 2, Nb</t>
+          <t>Getbergstjärn. Strycktjärn, N Piteå, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784017</v>
+        <v>784243</v>
       </c>
       <c r="R6" t="n">
-        <v>7288243</v>
+        <v>7288289</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,24 +1223,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426692</t>
+          <t>https://artportalen.se/Sighting/136621869</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136426693</v>
+        <v>136426692</v>
       </c>
       <c r="B7" t="n">
         <v>80589</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784037</v>
+        <v>784017</v>
       </c>
       <c r="R7" t="n">
-        <v>7288232</v>
+        <v>7288243</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,13 +1346,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426693</t>
+          <t>https://artportalen.se/Sighting/136426692</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136426701</v>
+        <v>136426693</v>
       </c>
       <c r="B8" t="n">
         <v>80589</v>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>784164</v>
+        <v>784037</v>
       </c>
       <c r="R8" t="n">
-        <v>7288253</v>
+        <v>7288232</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,38 +1458,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426701</t>
+          <t>https://artportalen.se/Sighting/136426693</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136426694</v>
+        <v>136426701</v>
       </c>
       <c r="B9" t="n">
-        <v>80594</v>
+        <v>80589</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>784036</v>
+        <v>784164</v>
       </c>
       <c r="R9" t="n">
-        <v>7288233</v>
+        <v>7288253</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,16 +1570,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426694</t>
+          <t>https://artportalen.se/Sighting/136426701</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136426687</v>
+        <v>136426694</v>
       </c>
       <c r="B10" t="n">
-        <v>99377</v>
+        <v>80594</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219874</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784094</v>
+        <v>784036</v>
       </c>
       <c r="R10" t="n">
-        <v>7288280</v>
+        <v>7288233</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,51 +1682,51 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426687</t>
+          <t>https://artportalen.se/Sighting/136426694</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136426686</v>
+        <v>136621873</v>
       </c>
       <c r="B11" t="n">
-        <v>99342</v>
+        <v>58003</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Getbergstjärn 2, Nb</t>
+          <t>Getbergstjärn. Strycktjärn, N Piteå, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784129</v>
+        <v>784043</v>
       </c>
       <c r="R11" t="n">
-        <v>7288247</v>
+        <v>7288283</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,49 +1783,49 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426686</t>
+          <t>https://artportalen.se/Sighting/136621873</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136426690</v>
+        <v>136426687</v>
       </c>
       <c r="B12" t="n">
-        <v>99342</v>
+        <v>99377</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784086</v>
+        <v>784094</v>
       </c>
       <c r="R12" t="n">
-        <v>7288273</v>
+        <v>7288280</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,13 +1906,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426690</t>
+          <t>https://artportalen.se/Sighting/136426687</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136426695</v>
+        <v>136426686</v>
       </c>
       <c r="B13" t="n">
         <v>99342</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>784034</v>
+        <v>784129</v>
       </c>
       <c r="R13" t="n">
-        <v>7288233</v>
+        <v>7288247</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,13 +2018,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426695</t>
+          <t>https://artportalen.se/Sighting/136426686</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136426696</v>
+        <v>136426690</v>
       </c>
       <c r="B14" t="n">
         <v>99342</v>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>784038</v>
+        <v>784086</v>
       </c>
       <c r="R14" t="n">
-        <v>7288225</v>
+        <v>7288273</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,13 +2130,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426696</t>
+          <t>https://artportalen.se/Sighting/136426690</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136426697</v>
+        <v>136426695</v>
       </c>
       <c r="B15" t="n">
         <v>99342</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>784073</v>
+        <v>784034</v>
       </c>
       <c r="R15" t="n">
-        <v>7288207</v>
+        <v>7288233</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:43</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:43</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,13 +2242,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426697</t>
+          <t>https://artportalen.se/Sighting/136426695</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136426713</v>
+        <v>136426696</v>
       </c>
       <c r="B16" t="n">
         <v>99342</v>
@@ -2276,26 +2276,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Getbergstjärn, Nb</t>
+          <t>Getbergstjärn 2, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>784191</v>
+        <v>784038</v>
       </c>
       <c r="R16" t="n">
-        <v>7288290</v>
+        <v>7288225</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2322,27 +2313,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:46</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>70tal blomstänglar</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,38 +2354,38 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426713</t>
+          <t>https://artportalen.se/Sighting/136426696</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136426691</v>
+        <v>136426697</v>
       </c>
       <c r="B17" t="n">
-        <v>99364</v>
+        <v>99342</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2409,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>784053</v>
+        <v>784073</v>
       </c>
       <c r="R17" t="n">
-        <v>7288267</v>
+        <v>7288207</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2444,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2454,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,51 +2466,60 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426691</t>
+          <t>https://artportalen.se/Sighting/136426697</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136426680</v>
+        <v>136426713</v>
       </c>
       <c r="B18" t="n">
-        <v>96554</v>
+        <v>99342</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2812</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Getbergstjärn 2, Nb</t>
+          <t>Getbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>784315</v>
+        <v>784191</v>
       </c>
       <c r="R18" t="n">
-        <v>7288340</v>
+        <v>7288290</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2551,22 +2546,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>70tal blomstänglar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2592,54 +2592,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426680</t>
+          <t>https://artportalen.se/Sighting/136426713</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136426681</v>
+        <v>136621875</v>
       </c>
       <c r="B19" t="n">
-        <v>96554</v>
+        <v>99342</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2812</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Getbergstjärn 2, Nb</t>
+          <t>Getbergstjärn. Strycktjärn, N Piteå, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>784300</v>
+        <v>784050</v>
       </c>
       <c r="R19" t="n">
-        <v>7288311</v>
+        <v>7288224</v>
       </c>
       <c r="S19" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2693,62 +2693,62 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426681</t>
+          <t>https://artportalen.se/Sighting/136621875</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136426712</v>
+        <v>136621876</v>
       </c>
       <c r="B20" t="n">
-        <v>96554</v>
+        <v>99342</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2812</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Getbergstjärn, Nb</t>
+          <t>Getbergstjärn. Strycktjärn, N Piteå, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>784256</v>
+        <v>784071</v>
       </c>
       <c r="R20" t="n">
-        <v>7288321</v>
+        <v>7288218</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2775,22 +2775,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2805,27 +2805,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426712</t>
+          <t>https://artportalen.se/Sighting/136621876</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136426710</v>
+        <v>136621877</v>
       </c>
       <c r="B21" t="n">
-        <v>79474</v>
+        <v>99342</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,34 +2833,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Getbergstjärn, Nb</t>
+          <t>Getbergstjärn. Strycktjärn, N Piteå, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>784283</v>
+        <v>784084</v>
       </c>
       <c r="R21" t="n">
-        <v>7288356</v>
+        <v>7288225</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2887,22 +2887,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Massor</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2917,18 +2922,1267 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136621877</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136621879</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Getbergstjärn. Strycktjärn, N Piteå, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>784111</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7288215</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136621879</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136426691</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99364</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Getbergstjärn 2, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>784053</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7288267</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136426691</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136426680</v>
+      </c>
+      <c r="B24" t="n">
+        <v>96554</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Getbergstjärn 2, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>784315</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7288340</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136426680</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136426681</v>
+      </c>
+      <c r="B25" t="n">
+        <v>96554</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Getbergstjärn 2, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>784300</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7288311</v>
+      </c>
+      <c r="S25" t="n">
+        <v>48</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136426681</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136426712</v>
+      </c>
+      <c r="B26" t="n">
+        <v>96554</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Getbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>784256</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7288321</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136426712</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136621862</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Getbergstjärn. Strycktjärn, N Piteå, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>784301</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7288320</v>
+      </c>
+      <c r="S27" t="n">
+        <v>9</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136621862</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136621870</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93436</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Getbergstjärn. Strycktjärn, N Piteå, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>784240</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7288292</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136621870</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136426710</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79474</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Getbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>784283</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7288356</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136426710</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136621871</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80594</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Getbergstjärn. Strycktjärn, N Piteå, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>784094</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7288296</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136621871</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136621868</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Getbergstjärn. Strycktjärn, N Piteå, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>784301</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7288353</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136621868</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136621861</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Getbergstjärn. Strycktjärn, N Piteå, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>784284</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7288325</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136621861</t>
         </is>
       </c>
     </row>
@@ -2954,6 +4208,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136426698</v>
       </c>
       <c r="B2" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136426699</v>
       </c>
       <c r="B3" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136426685</v>
       </c>
       <c r="B4" t="n">
-        <v>96554</v>
+        <v>96557</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136426688</v>
       </c>
       <c r="B5" t="n">
-        <v>96554</v>
+        <v>96557</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136621869</v>
       </c>
       <c r="B6" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136426687</v>
       </c>
       <c r="B12" t="n">
-        <v>99377</v>
+        <v>99380</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136426686</v>
       </c>
       <c r="B13" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136426690</v>
       </c>
       <c r="B14" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136426695</v>
       </c>
       <c r="B15" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136426696</v>
       </c>
       <c r="B16" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136426697</v>
       </c>
       <c r="B17" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136426713</v>
       </c>
       <c r="B18" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136621875</v>
       </c>
       <c r="B19" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>136621876</v>
       </c>
       <c r="B20" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136621877</v>
       </c>
       <c r="B21" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>136621879</v>
       </c>
       <c r="B22" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136426691</v>
       </c>
       <c r="B23" t="n">
-        <v>99364</v>
+        <v>99367</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>136426680</v>
       </c>
       <c r="B24" t="n">
-        <v>96554</v>
+        <v>96557</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136426681</v>
       </c>
       <c r="B25" t="n">
-        <v>96554</v>
+        <v>96557</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>136426712</v>
       </c>
       <c r="B26" t="n">
-        <v>96554</v>
+        <v>96557</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136621862</v>
       </c>
       <c r="B27" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>136621870</v>
       </c>
       <c r="B28" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136621861</v>
       </c>
       <c r="B32" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136426698</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136426699</v>
       </c>
       <c r="B3" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136426685</v>
       </c>
       <c r="B4" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136426688</v>
       </c>
       <c r="B5" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136426687</v>
       </c>
       <c r="B12" t="n">
-        <v>99380</v>
+        <v>99381</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136426686</v>
       </c>
       <c r="B13" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136426690</v>
       </c>
       <c r="B14" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136426695</v>
       </c>
       <c r="B15" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136426696</v>
       </c>
       <c r="B16" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136426697</v>
       </c>
       <c r="B17" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136426713</v>
       </c>
       <c r="B18" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136621875</v>
       </c>
       <c r="B19" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>136621876</v>
       </c>
       <c r="B20" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136621877</v>
       </c>
       <c r="B21" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>136621879</v>
       </c>
       <c r="B22" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136426691</v>
       </c>
       <c r="B23" t="n">
-        <v>99367</v>
+        <v>99368</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>136426680</v>
       </c>
       <c r="B24" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136426681</v>
       </c>
       <c r="B25" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>136426712</v>
       </c>
       <c r="B26" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>136621870</v>
       </c>
       <c r="B28" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136621861</v>
       </c>
       <c r="B32" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136426698</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136426699</v>
       </c>
       <c r="B3" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136426685</v>
       </c>
       <c r="B4" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136426688</v>
       </c>
       <c r="B5" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136621869</v>
       </c>
       <c r="B6" t="n">
-        <v>91542</v>
+        <v>91544</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136426692</v>
       </c>
       <c r="B7" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136426693</v>
       </c>
       <c r="B8" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136426701</v>
       </c>
       <c r="B9" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136426694</v>
       </c>
       <c r="B10" t="n">
-        <v>80594</v>
+        <v>80596</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136621873</v>
       </c>
       <c r="B11" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136426687</v>
       </c>
       <c r="B12" t="n">
-        <v>99381</v>
+        <v>99386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136426686</v>
       </c>
       <c r="B13" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136426690</v>
       </c>
       <c r="B14" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136426695</v>
       </c>
       <c r="B15" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136426696</v>
       </c>
       <c r="B16" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136426697</v>
       </c>
       <c r="B17" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136426713</v>
       </c>
       <c r="B18" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136621875</v>
       </c>
       <c r="B19" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>136621876</v>
       </c>
       <c r="B20" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136621877</v>
       </c>
       <c r="B21" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>136621879</v>
       </c>
       <c r="B22" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136426691</v>
       </c>
       <c r="B23" t="n">
-        <v>99368</v>
+        <v>99373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>136426680</v>
       </c>
       <c r="B24" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136426681</v>
       </c>
       <c r="B25" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>136426712</v>
       </c>
       <c r="B26" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136621862</v>
       </c>
       <c r="B27" t="n">
-        <v>91542</v>
+        <v>91544</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>136621870</v>
       </c>
       <c r="B28" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>136426710</v>
       </c>
       <c r="B29" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>136621871</v>
       </c>
       <c r="B30" t="n">
-        <v>80594</v>
+        <v>80596</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>136621868</v>
       </c>
       <c r="B31" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136621861</v>
       </c>
       <c r="B32" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136426698</v>
       </c>
       <c r="B2" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136426699</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136426685</v>
       </c>
       <c r="B4" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136426688</v>
       </c>
       <c r="B5" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136621869</v>
       </c>
       <c r="B6" t="n">
-        <v>91544</v>
+        <v>91546</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136426687</v>
       </c>
       <c r="B12" t="n">
-        <v>99386</v>
+        <v>99388</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136426686</v>
       </c>
       <c r="B13" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136426690</v>
       </c>
       <c r="B14" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136426695</v>
       </c>
       <c r="B15" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136426696</v>
       </c>
       <c r="B16" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136426697</v>
       </c>
       <c r="B17" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136426713</v>
       </c>
       <c r="B18" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136621875</v>
       </c>
       <c r="B19" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>136621876</v>
       </c>
       <c r="B20" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136621877</v>
       </c>
       <c r="B21" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>136621879</v>
       </c>
       <c r="B22" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136426691</v>
       </c>
       <c r="B23" t="n">
-        <v>99373</v>
+        <v>99375</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>136426680</v>
       </c>
       <c r="B24" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136426681</v>
       </c>
       <c r="B25" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>136426712</v>
       </c>
       <c r="B26" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136621862</v>
       </c>
       <c r="B27" t="n">
-        <v>91544</v>
+        <v>91546</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>136621870</v>
       </c>
       <c r="B28" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136621861</v>
       </c>
       <c r="B32" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136426698</v>
       </c>
       <c r="B2" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136426699</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136426685</v>
       </c>
       <c r="B4" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136426688</v>
       </c>
       <c r="B5" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136621869</v>
       </c>
       <c r="B6" t="n">
-        <v>91546</v>
+        <v>91548</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136426692</v>
       </c>
       <c r="B7" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136426693</v>
       </c>
       <c r="B8" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136426701</v>
       </c>
       <c r="B9" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136426694</v>
       </c>
       <c r="B10" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136426687</v>
       </c>
       <c r="B12" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136426686</v>
       </c>
       <c r="B13" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136426690</v>
       </c>
       <c r="B14" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136426695</v>
       </c>
       <c r="B15" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136426696</v>
       </c>
       <c r="B16" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136426697</v>
       </c>
       <c r="B17" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136426713</v>
       </c>
       <c r="B18" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136621875</v>
       </c>
       <c r="B19" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>136621876</v>
       </c>
       <c r="B20" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136621877</v>
       </c>
       <c r="B21" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>136621879</v>
       </c>
       <c r="B22" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136426691</v>
       </c>
       <c r="B23" t="n">
-        <v>99375</v>
+        <v>99381</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>136426680</v>
       </c>
       <c r="B24" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136426681</v>
       </c>
       <c r="B25" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>136426712</v>
       </c>
       <c r="B26" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136621862</v>
       </c>
       <c r="B27" t="n">
-        <v>91546</v>
+        <v>91548</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>136621870</v>
       </c>
       <c r="B28" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>136426710</v>
       </c>
       <c r="B29" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>136621871</v>
       </c>
       <c r="B30" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136621861</v>
       </c>
       <c r="B32" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136426698</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136426699</v>
       </c>
       <c r="B3" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136426685</v>
       </c>
       <c r="B4" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136426688</v>
       </c>
       <c r="B5" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136621869</v>
       </c>
       <c r="B6" t="n">
-        <v>91548</v>
+        <v>91550</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136426692</v>
       </c>
       <c r="B7" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136426693</v>
       </c>
       <c r="B8" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136426701</v>
       </c>
       <c r="B9" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136426694</v>
       </c>
       <c r="B10" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136426687</v>
       </c>
       <c r="B12" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136426686</v>
       </c>
       <c r="B13" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136426690</v>
       </c>
       <c r="B14" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136426695</v>
       </c>
       <c r="B15" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136426696</v>
       </c>
       <c r="B16" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136426697</v>
       </c>
       <c r="B17" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136426713</v>
       </c>
       <c r="B18" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136621875</v>
       </c>
       <c r="B19" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>136621876</v>
       </c>
       <c r="B20" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136621877</v>
       </c>
       <c r="B21" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>136621879</v>
       </c>
       <c r="B22" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136426691</v>
       </c>
       <c r="B23" t="n">
-        <v>99381</v>
+        <v>99383</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>136426680</v>
       </c>
       <c r="B24" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136426681</v>
       </c>
       <c r="B25" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>136426712</v>
       </c>
       <c r="B26" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136621862</v>
       </c>
       <c r="B27" t="n">
-        <v>91548</v>
+        <v>91550</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>136621870</v>
       </c>
       <c r="B28" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>136426710</v>
       </c>
       <c r="B29" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>136621871</v>
       </c>
       <c r="B30" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136621861</v>
       </c>
       <c r="B32" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136426698</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136426699</v>
       </c>
       <c r="B3" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136426685</v>
       </c>
       <c r="B4" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136426688</v>
       </c>
       <c r="B5" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136621869</v>
       </c>
       <c r="B6" t="n">
-        <v>91550</v>
+        <v>91551</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136426692</v>
       </c>
       <c r="B7" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136426693</v>
       </c>
       <c r="B8" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136426701</v>
       </c>
       <c r="B9" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136426694</v>
       </c>
       <c r="B10" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136426687</v>
       </c>
       <c r="B12" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136426686</v>
       </c>
       <c r="B13" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136426690</v>
       </c>
       <c r="B14" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136426695</v>
       </c>
       <c r="B15" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136426696</v>
       </c>
       <c r="B16" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136426697</v>
       </c>
       <c r="B17" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136426713</v>
       </c>
       <c r="B18" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136621875</v>
       </c>
       <c r="B19" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>136621876</v>
       </c>
       <c r="B20" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136621877</v>
       </c>
       <c r="B21" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>136621879</v>
       </c>
       <c r="B22" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136426691</v>
       </c>
       <c r="B23" t="n">
-        <v>99383</v>
+        <v>99384</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>136426680</v>
       </c>
       <c r="B24" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136426681</v>
       </c>
       <c r="B25" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>136426712</v>
       </c>
       <c r="B26" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136621862</v>
       </c>
       <c r="B27" t="n">
-        <v>91550</v>
+        <v>91551</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>136621870</v>
       </c>
       <c r="B28" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>136426710</v>
       </c>
       <c r="B29" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>136621871</v>
       </c>
       <c r="B30" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136621861</v>
       </c>
       <c r="B32" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136426698</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136426699</v>
       </c>
       <c r="B3" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136426685</v>
       </c>
       <c r="B4" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136426688</v>
       </c>
       <c r="B5" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136621869</v>
       </c>
       <c r="B6" t="n">
-        <v>91551</v>
+        <v>91557</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136426687</v>
       </c>
       <c r="B12" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136426686</v>
       </c>
       <c r="B13" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136426690</v>
       </c>
       <c r="B14" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136426695</v>
       </c>
       <c r="B15" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136426696</v>
       </c>
       <c r="B16" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136426697</v>
       </c>
       <c r="B17" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136426713</v>
       </c>
       <c r="B18" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136621875</v>
       </c>
       <c r="B19" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>136621876</v>
       </c>
       <c r="B20" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136621877</v>
       </c>
       <c r="B21" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>136621879</v>
       </c>
       <c r="B22" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136426691</v>
       </c>
       <c r="B23" t="n">
-        <v>99384</v>
+        <v>99390</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>136426680</v>
       </c>
       <c r="B24" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136426681</v>
       </c>
       <c r="B25" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>136426712</v>
       </c>
       <c r="B26" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136621862</v>
       </c>
       <c r="B27" t="n">
-        <v>91551</v>
+        <v>91557</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>136621870</v>
       </c>
       <c r="B28" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136621861</v>
       </c>
       <c r="B32" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136426698</v>
       </c>
       <c r="B2" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136426699</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136426685</v>
       </c>
       <c r="B4" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136426688</v>
       </c>
       <c r="B5" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136621869</v>
       </c>
       <c r="B6" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136426692</v>
       </c>
       <c r="B7" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136426693</v>
       </c>
       <c r="B8" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136426701</v>
       </c>
       <c r="B9" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136426694</v>
       </c>
       <c r="B10" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136426687</v>
       </c>
       <c r="B12" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136426686</v>
       </c>
       <c r="B13" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136426690</v>
       </c>
       <c r="B14" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136426695</v>
       </c>
       <c r="B15" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136426696</v>
       </c>
       <c r="B16" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136426697</v>
       </c>
       <c r="B17" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136426713</v>
       </c>
       <c r="B18" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136621875</v>
       </c>
       <c r="B19" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>136621876</v>
       </c>
       <c r="B20" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136621877</v>
       </c>
       <c r="B21" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>136621879</v>
       </c>
       <c r="B22" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136426691</v>
       </c>
       <c r="B23" t="n">
-        <v>99390</v>
+        <v>99394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>136426680</v>
       </c>
       <c r="B24" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136426681</v>
       </c>
       <c r="B25" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>136426712</v>
       </c>
       <c r="B26" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136621862</v>
       </c>
       <c r="B27" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>136621870</v>
       </c>
       <c r="B28" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>136426710</v>
       </c>
       <c r="B29" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>136621871</v>
       </c>
       <c r="B30" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136621861</v>
       </c>
       <c r="B32" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -2601,7 +2601,7 @@
         <v>136621875</v>
       </c>
       <c r="B19" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>136621876</v>
       </c>
       <c r="B20" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136621877</v>
       </c>
       <c r="B21" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>136621879</v>
       </c>
       <c r="B22" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136621861</v>
       </c>
       <c r="B32" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>136621869</v>
       </c>
       <c r="B6" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136621875</v>
       </c>
       <c r="B19" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>136621876</v>
       </c>
       <c r="B20" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136621877</v>
       </c>
       <c r="B21" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>136621879</v>
       </c>
       <c r="B22" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136621862</v>
       </c>
       <c r="B27" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>136621870</v>
       </c>
       <c r="B28" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>136621871</v>
       </c>
       <c r="B30" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136621861</v>
       </c>
       <c r="B32" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>136621869</v>
       </c>
       <c r="B6" t="n">
-        <v>91563</v>
+        <v>91576</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136621873</v>
       </c>
       <c r="B11" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136621875</v>
       </c>
       <c r="B19" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>136621876</v>
       </c>
       <c r="B20" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136621877</v>
       </c>
       <c r="B21" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>136621879</v>
       </c>
       <c r="B22" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136621862</v>
       </c>
       <c r="B27" t="n">
-        <v>91563</v>
+        <v>91576</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>136621870</v>
       </c>
       <c r="B28" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>136621871</v>
       </c>
       <c r="B30" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>136621868</v>
       </c>
       <c r="B31" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136621861</v>
       </c>
       <c r="B32" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>136621869</v>
       </c>
       <c r="B6" t="n">
-        <v>91576</v>
+        <v>91578</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136621873</v>
       </c>
       <c r="B11" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136621875</v>
       </c>
       <c r="B19" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>136621876</v>
       </c>
       <c r="B20" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136621877</v>
       </c>
       <c r="B21" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>136621879</v>
       </c>
       <c r="B22" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136621862</v>
       </c>
       <c r="B27" t="n">
-        <v>91576</v>
+        <v>91578</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>136621870</v>
       </c>
       <c r="B28" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>136621871</v>
       </c>
       <c r="B30" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>136621868</v>
       </c>
       <c r="B31" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136621861</v>
       </c>
       <c r="B32" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -3982,11 +3982,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>136621869</v>
       </c>
       <c r="B6" t="n">
-        <v>91578</v>
+        <v>91581</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136621875</v>
       </c>
       <c r="B19" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>136621876</v>
       </c>
       <c r="B20" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136621877</v>
       </c>
       <c r="B21" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>136621879</v>
       </c>
       <c r="B22" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136621862</v>
       </c>
       <c r="B27" t="n">
-        <v>91578</v>
+        <v>91581</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>136621870</v>
       </c>
       <c r="B28" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>136621861</v>
       </c>
       <c r="B32" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3163,32 +3163,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136426680</v>
+        <v>136426684</v>
       </c>
       <c r="B24" t="n">
-        <v>96584</v>
+        <v>92561</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2812</v>
+        <v>6040186</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>784315</v>
+        <v>784217</v>
       </c>
       <c r="R24" t="n">
-        <v>7288340</v>
+        <v>7288278</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3252,6 +3252,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3269,13 +3270,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426680</t>
+          <t>https://artportalen.se/Sighting/136426684</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136426681</v>
+        <v>136426680</v>
       </c>
       <c r="B25" t="n">
         <v>96584</v>
@@ -3310,13 +3311,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>784300</v>
+        <v>784315</v>
       </c>
       <c r="R25" t="n">
-        <v>7288311</v>
+        <v>7288340</v>
       </c>
       <c r="S25" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3345,7 +3346,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3355,7 +3356,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3381,13 +3382,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426681</t>
+          <t>https://artportalen.se/Sighting/136426680</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136426712</v>
+        <v>136426681</v>
       </c>
       <c r="B26" t="n">
         <v>96584</v>
@@ -3418,17 +3419,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Getbergstjärn, Nb</t>
+          <t>Getbergstjärn 2, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>784256</v>
+        <v>784300</v>
       </c>
       <c r="R26" t="n">
-        <v>7288321</v>
+        <v>7288311</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3452,22 +3453,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3493,54 +3494,54 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426712</t>
+          <t>https://artportalen.se/Sighting/136426681</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136621862</v>
+        <v>136426712</v>
       </c>
       <c r="B27" t="n">
-        <v>91581</v>
+        <v>96584</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3286</v>
+        <v>2812</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Getbergstjärn. Strycktjärn, N Piteå, Nb</t>
+          <t>Getbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>784301</v>
+        <v>784256</v>
       </c>
       <c r="R27" t="n">
-        <v>7288320</v>
+        <v>7288321</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3569,7 +3570,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,7 +3580,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3594,27 +3595,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136621862</t>
+          <t>https://artportalen.se/Sighting/136426712</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136621870</v>
+        <v>136621862</v>
       </c>
       <c r="B28" t="n">
-        <v>93481</v>
+        <v>91581</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3622,40 +3623,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5964</v>
+        <v>3286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Getbergstjärn. Strycktjärn, N Piteå, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>784240</v>
+        <v>784301</v>
       </c>
       <c r="R28" t="n">
-        <v>7288292</v>
+        <v>7288320</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3679,22 +3677,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3703,7 +3701,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3721,51 +3718,54 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136621870</t>
+          <t>https://artportalen.se/Sighting/136621862</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136426710</v>
+        <v>136621870</v>
       </c>
       <c r="B29" t="n">
-        <v>79485</v>
+        <v>93481</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Getbergstjärn, Nb</t>
+          <t>Getbergstjärn. Strycktjärn, N Piteå, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>784283</v>
+        <v>784240</v>
       </c>
       <c r="R29" t="n">
-        <v>7288356</v>
+        <v>7288292</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3792,22 +3792,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3816,68 +3816,69 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136426710</t>
+          <t>https://artportalen.se/Sighting/136621870</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136621871</v>
+        <v>136426710</v>
       </c>
       <c r="B30" t="n">
-        <v>80623</v>
+        <v>79485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Getbergstjärn. Strycktjärn, N Piteå, Nb</t>
+          <t>Getbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>784094</v>
+        <v>784283</v>
       </c>
       <c r="R30" t="n">
-        <v>7288296</v>
+        <v>7288356</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3904,22 +3905,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3934,66 +3935,62 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136621871</t>
+          <t>https://artportalen.se/Sighting/136426710</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136621868</v>
+        <v>136621871</v>
       </c>
       <c r="B31" t="n">
-        <v>58184</v>
+        <v>80623</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Getbergstjärn. Strycktjärn, N Piteå, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>784301</v>
+        <v>784094</v>
       </c>
       <c r="R31" t="n">
-        <v>7288353</v>
+        <v>7288296</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4025,7 +4022,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4035,7 +4032,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4061,44 +4058,44 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136621868</t>
+          <t>https://artportalen.se/Sighting/136621871</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136621861</v>
+        <v>136621868</v>
       </c>
       <c r="B32" t="n">
-        <v>99394</v>
+        <v>58184</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4106,10 +4103,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>784284</v>
+        <v>784301</v>
       </c>
       <c r="R32" t="n">
-        <v>7288325</v>
+        <v>7288353</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4136,22 +4133,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4160,7 +4157,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4178,7 +4174,253 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136621868</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136621861</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99394</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Getbergstjärn. Strycktjärn, N Piteå, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>784284</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7288325</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136621861</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136426683</v>
+      </c>
+      <c r="B34" t="n">
+        <v>87461</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6038612</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Koboltspindling</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cortinarius cobaltinus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Getbergstjärn 2, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>784248</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7288296</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>KOH  hattkant; positiv, jordgubbssaft Bulbkant; positiv, jordgubbssaft Basalmycel; positiv, "tuschpennerosa" Mycelsträng; positiv, "tuschpennerosa" Köttsida fot, negativ, (blek gul/beige/rosa ton Granskog, örtrikt, friskmossor,</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136426683</t>
         </is>
       </c>
     </row>
@@ -4215,6 +4457,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -3166,7 +3166,7 @@
         <v>136426684</v>
       </c>
       <c r="B24" t="n">
-        <v>92561</v>
+        <v>92573</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>136426683</v>
       </c>
       <c r="B34" t="n">
-        <v>87461</v>
+        <v>87472</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -3166,7 +3166,7 @@
         <v>136426684</v>
       </c>
       <c r="B24" t="n">
-        <v>92573</v>
+        <v>92574</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>136426683</v>
       </c>
       <c r="B34" t="n">
-        <v>87472</v>
+        <v>87473</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -3166,7 +3166,7 @@
         <v>136426684</v>
       </c>
       <c r="B24" t="n">
-        <v>92574</v>
+        <v>92577</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>136426683</v>
       </c>
       <c r="B34" t="n">
-        <v>87473</v>
+        <v>87476</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -3166,7 +3166,7 @@
         <v>136426684</v>
       </c>
       <c r="B24" t="n">
-        <v>92577</v>
+        <v>92581</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>136426683</v>
       </c>
       <c r="B34" t="n">
-        <v>87476</v>
+        <v>87480</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
